--- a/experiments/rain_experiments.xlsx
+++ b/experiments/rain_experiments.xlsx
@@ -226,8 +226,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SleetExperiments" displayName="SleetExperiments" ref="A1:L7" totalsRowShown="0">
-  <autoFilter ref="A1:L7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SleetExperiments" displayName="SleetExperiments" ref="A1:L16" totalsRowShown="0">
+  <autoFilter ref="A1:L16">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -261,7 +261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -329,23 +329,35 @@
       <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>17</v>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>45.8805</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>25.6088</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>54.0046</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>34.1339</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>8.1241</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>8.5251</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -367,23 +379,35 @@
       <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>17</v>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>44.3212</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>26.7730</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>69.8328</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>45.8413</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>25.5116</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>19.0683</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -405,23 +429,35 @@
       <c r="F4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>17</v>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>28.8668</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>23.5785</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>53.3106</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>40.2347</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>24.4438</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>16.6562</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -443,23 +479,35 @@
       <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>17</v>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>40.2097</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>22.3310</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>56.4281</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>34.8202</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>16.2184</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>12.4892</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -481,23 +529,35 @@
       <c r="F6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>17</v>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>43.8184</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>26.9076</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>67.6824</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>43.7780</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>23.8640</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>16.8704</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -519,65 +579,569 @@
       <c r="F7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>24.6295</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>20.2679</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>53.1439</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>40.2587</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>28.5144</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>19.9908</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>group7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>41.9427</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>23.8003</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>50.7081</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>31.4970</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>8.7654</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>7.6967</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>group8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>47.8281</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>27.3316</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>69.2378</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>45.0316</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>21.4097</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>17.7000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>group9</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>26.3945</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>20.7545</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>52.7525</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>41.3121</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>26.3580</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>20.5576</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>group10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>39.9978</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>22.5385</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>50.6894</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>31.4579</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>10.6916</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>8.9194</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>group11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>36.7271</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>21.9962</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>69.5499</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>45.7638</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>32.8228</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>23.7676</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>group12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>24.7254</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>20.5046</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>52.3635</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>41.7569</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>27.6381</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>21.2523</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>group16</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>47.6360</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>22.8276</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>54.0166</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>35.4717</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>6.3806</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>12.6441</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>group17</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>46.4622</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>27.3649</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>68.0758</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>44.3267</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>21.6136</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>16.9618</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>group18</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>26.1121</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>21.0727</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>48.9116</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>36.9275</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>22.7995</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>15.8548</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>average(15)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="E17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="F17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="J17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>17</v>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>20.3437</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>15.9303</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:L16"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <tableParts count="1">
